--- a/artfynd/A 60419-2024 artfynd.xlsx
+++ b/artfynd/A 60419-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>90799038</v>
+        <v>91131091</v>
       </c>
       <c r="B2" t="n">
-        <v>96660</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99017</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219880</v>
+        <v>219795</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bleckåsån-Höstbodarna, Jmt</t>
+          <t>Halbodarna_SÖ, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>435073.901796468</v>
+        <v>435123</v>
       </c>
       <c r="R2" t="n">
-        <v>7033255.029223522</v>
+        <v>7033365</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2019-07-24</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-07-24</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,11 +756,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Möjlig kalktallskog</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -796,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>91131090</v>
+        <v>90799038</v>
       </c>
       <c r="B3" t="n">
-        <v>96660</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99456</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -832,14 +807,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Halbodarna_SÖ, Jmt</t>
+          <t>Bleckåsån-Höstbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>435122.7856273972</v>
+        <v>435074</v>
       </c>
       <c r="R3" t="n">
-        <v>7033365.127105075</v>
+        <v>7033255</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -869,19 +844,9 @@
           <t>2019-07-24</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2019-07-24</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,6 +857,11 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Möjlig kalktallskog</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -912,15 +882,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>91131091</v>
+        <v>91131090</v>
       </c>
       <c r="B4" t="n">
-        <v>96232</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99456</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -928,21 +893,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219795</v>
+        <v>219880</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -952,10 +917,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>435122.7856273972</v>
+        <v>435123</v>
       </c>
       <c r="R4" t="n">
-        <v>7033365.127105075</v>
+        <v>7033365</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -985,19 +950,9 @@
           <t>2019-07-24</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2019-07-24</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 60419-2024 artfynd.xlsx
+++ b/artfynd/A 60419-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91131091</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,6 +889,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90799038</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -980,8 +995,18 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91131090</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>